--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_11_R2.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_11_R2.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4274</v>
+        <v>7.5522</v>
       </c>
       <c r="E2" t="n">
-        <v>9.610799999999999</v>
+        <v>9.567500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.1834</v>
+        <v>-2.0153</v>
       </c>
       <c r="G2" t="n">
         <v>5.1553</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0294</v>
+        <v>0.0953</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0578</v>
+        <v>1.0146</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0873</v>
+        <v>-0.9192</v>
       </c>
       <c r="V2" t="n">
         <v>0.6778999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1173</v>
+        <v>4.7526</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4165</v>
+        <v>4.119</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7008</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>3.8857</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7677</v>
+        <v>0.4031</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9109</v>
+        <v>0.6135</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1432</v>
+        <v>-0.2104</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6877</v>
+        <v>3.5704</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0602</v>
+        <v>3.1781</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.3922</v>
       </c>
       <c r="G4" t="n">
         <v>3.6902</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.322</v>
+        <v>-0.4393</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0272</v>
+        <v>0.0907</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2948</v>
+        <v>-0.53</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0722</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9523</v>
+        <v>2.5414</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6861</v>
+        <v>2.04</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2661</v>
+        <v>0.5014</v>
       </c>
       <c r="G5" t="n">
         <v>5.0841</v>
@@ -844,13 +844,13 @@
         <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0776</v>
+        <v>-0.4885</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6642</v>
+        <v>-0.3104</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4134</v>
+        <v>-0.1781</v>
       </c>
       <c r="V5" t="n">
         <v>-2.2862</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.081</v>
+        <v>1.1886</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5005</v>
+        <v>2.3392</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4195</v>
+        <v>-1.1506</v>
       </c>
       <c r="G6" t="n">
         <v>0.0328</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1204</v>
+        <v>0.228</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5702</v>
+        <v>0.409</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4498</v>
+        <v>-0.181</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2251</v>
+        <v>-0.0369</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2454</v>
+        <v>-0.4066</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4705</v>
+        <v>0.3697</v>
       </c>
       <c r="G7" t="n">
         <v>-0.313</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3062</v>
+        <v>0.0442</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4129</v>
+        <v>0.2517</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1067</v>
+        <v>-0.2076</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3192</v>
+        <v>-0.4132</v>
       </c>
       <c r="E8" t="n">
-        <v>1.533</v>
+        <v>1.3717</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8522</v>
+        <v>-1.7849</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4621</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1792</v>
+        <v>-0.2732</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5623</v>
+        <v>0.4011</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7415</v>
+        <v>-0.6743</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3316</v>
+        <v>-0.4661</v>
       </c>
       <c r="E9" t="n">
         <v>0.0036</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3353</v>
+        <v>-0.4697</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4765</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.217</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0668</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2838</v>
+        <v>0.1494</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5361</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4178</v>
+        <v>-0.6525</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5934</v>
+        <v>2.2579</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0112</v>
+        <v>-2.9104</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8821</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9274</v>
+        <v>-0.1621</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3655</v>
+        <v>0.2989</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5619</v>
+        <v>-0.461</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5361</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5304</v>
+        <v>-1.8937</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2354</v>
+        <v>-0.0511</v>
       </c>
       <c r="F11" t="n">
-        <v>0.705</v>
+        <v>-1.8426</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2987</v>
+        <v>-0.5396</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0048</v>
+        <v>-0.9712</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.4316</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7669</v>
+        <v>0.9155</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9509</v>
+        <v>0.4271</v>
       </c>
       <c r="L11" t="n">
-        <v>0.184</v>
+        <v>0.4884</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4681</v>
+        <v>-1.4551</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0539</v>
+        <v>-1.3983</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5221</v>
+        <v>-0.0568</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7683</v>
+        <v>-0.1375</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2908</v>
+        <v>0.0514</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0592</v>
+        <v>-0.1889</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6083</v>
+        <v>-2.1444</v>
       </c>
       <c r="W11" t="n">
         <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7501</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>X. RATHAN-MAYES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7358</v>
+        <v>-2.6278</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7588</v>
+        <v>-3.4686</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.977</v>
+        <v>0.8408</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5396</v>
+        <v>-2.4197</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9712</v>
+        <v>0.0095</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4316</v>
+        <v>-2.4293</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9155</v>
+        <v>-1.9119</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4271</v>
+        <v>0.4103</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4884</v>
+        <v>-2.3222</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4551</v>
+        <v>-0.5078</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3983</v>
+        <v>-0.4008</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0568</v>
+        <v>-0.107</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9796</v>
+        <v>-0.226</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6563</v>
+        <v>-0.3969</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3233</v>
+        <v>0.1709</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1444</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.2862</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X. RATHAN-MAYES</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.813</v>
+        <v>-2.7986</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5865</v>
+        <v>-2.9995</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7736</v>
+        <v>0.2009</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.4197</v>
+        <v>-0.2987</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0095</v>
+        <v>-1.0048</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.4293</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9119</v>
+        <v>-0.7669</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4103</v>
+        <v>-0.9509</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.3222</v>
+        <v>0.184</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5078</v>
+        <v>0.4681</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4008</v>
+        <v>-0.0539</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.107</v>
+        <v>0.5221</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4112</v>
+        <v>0.5001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5149</v>
+        <v>-0.0549</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1037</v>
+        <v>0.5551</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.6083</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="14">
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.343</v>
+        <v>10.7164</v>
       </c>
       <c r="E14" t="n">
-        <v>17.578</v>
+        <v>17.9512</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.235099999999999</v>
+        <v>-7.234900000000001</v>
       </c>
       <c r="G14" t="n">
         <v>12.4564</v>
       </c>
       <c r="H14" t="n">
-        <v>7.454400000000001</v>
+        <v>7.4544</v>
       </c>
       <c r="I14" t="n">
-        <v>5.001900000000001</v>
+        <v>5.0019</v>
       </c>
       <c r="J14" t="n">
         <v>23.9119</v>
@@ -1531,7 +1531,7 @@
         <v>-11.4554</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.848100000000001</v>
+        <v>-4.8481</v>
       </c>
       <c r="O14" t="n">
         <v>-6.6073</v>
@@ -1546,13 +1546,13 @@
         <v>17.3965</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7468</v>
+        <v>-0.3733</v>
       </c>
       <c r="T14" t="n">
-        <v>1.928400000000001</v>
+        <v>2.3019</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.6752</v>
+        <v>-2.6751</v>
       </c>
       <c r="V14" t="n">
         <v>-8.325100000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9635</v>
+        <v>5.5819</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8784</v>
+        <v>6.3502</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.7683</v>
       </c>
       <c r="G15" t="n">
         <v>0.1118</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2614</v>
+        <v>0.8797</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3339</v>
+        <v>0.1379</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.7418</v>
       </c>
       <c r="V15" t="n">
         <v>3.8945</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8103</v>
+        <v>1.6873</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3981</v>
+        <v>4.1622</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5879</v>
+        <v>-2.475</v>
       </c>
       <c r="G16" t="n">
         <v>-2.7303</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1668</v>
+        <v>1.0438</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7512</v>
+        <v>0.5153</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4156</v>
+        <v>0.5285</v>
       </c>
       <c r="V16" t="n">
         <v>1.7501</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7579</v>
+        <v>0.1111</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9789</v>
+        <v>0.6814</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.221</v>
+        <v>-0.5704</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7559</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2819</v>
+        <v>0.635</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6869</v>
+        <v>0.3894</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.405</v>
+        <v>0.2456</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.408</v>
+        <v>-1.6611</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6778</v>
+        <v>0.324</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0859</v>
+        <v>-1.9851</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9395</v>
@@ -1858,13 +1858,13 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0742</v>
+        <v>-0.3273</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5702</v>
+        <v>0.2164</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6445</v>
+        <v>-0.5436</v>
       </c>
       <c r="V18" t="n">
         <v>0.1418</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DAVIDOVAC</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1583</v>
+        <v>-1.7192</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8735000000000001</v>
+        <v>1.0862</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0318</v>
+        <v>-2.8054</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8904</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2844</v>
+        <v>-2.1764</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.606</v>
+        <v>1.2112</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8260999999999999</v>
+        <v>3.4379</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4284</v>
+        <v>-0.4097</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6022999999999999</v>
+        <v>3.8476</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7165</v>
+        <v>-4.4031</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7128</v>
+        <v>-1.7667</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0037</v>
+        <v>-2.6364</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3378</v>
+        <v>0.0294</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2072</v>
+        <v>0.0553</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8694</v>
+        <v>-0.0259</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>D. DAVIDOVAC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7757</v>
+        <v>-2.3948</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1426</v>
+        <v>0.4017</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9183</v>
+        <v>-2.7966</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-1.8904</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1764</v>
+        <v>-0.2844</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2112</v>
+        <v>-1.606</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4379</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4097</v>
+        <v>1.4284</v>
       </c>
       <c r="L20" t="n">
-        <v>3.8476</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.4031</v>
+        <v>-2.7165</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7667</v>
+        <v>-1.7128</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.6364</v>
+        <v>-1.0037</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8556</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0271</v>
+        <v>0.1013</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8883</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1388</v>
+        <v>-0.6341</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7136</v>
+        <v>-3.5227</v>
       </c>
       <c r="E21" t="n">
         <v>-0.9099</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8037</v>
+        <v>-2.6129</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6919999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3826</v>
+        <v>-0.1918</v>
       </c>
       <c r="T21" t="n">
         <v>0.3462</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7288</v>
+        <v>-0.5379</v>
       </c>
       <c r="V21" t="n">
         <v>1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.8192</v>
+        <v>-6.8527</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.8046</v>
+        <v>-4.861</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0145</v>
+        <v>-1.9917</v>
       </c>
       <c r="G22" t="n">
         <v>-3.595</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8171</v>
+        <v>0.1494</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6642</v>
+        <v>0.2794</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1529</v>
+        <v>-0.13</v>
       </c>
       <c r="V22" t="n">
         <v>0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.3431</v>
+        <v>-8.770199999999999</v>
       </c>
       <c r="E23" t="n">
         <v>7.234799999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-17.5779</v>
+        <v>-16.0054</v>
       </c>
       <c r="G23" t="n">
         <v>-12.4565</v>
@@ -2248,13 +2248,13 @@
         <v>10.4379</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7469000000000006</v>
+        <v>2.3195</v>
       </c>
       <c r="T23" t="n">
         <v>2.6753</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.9285</v>
+        <v>-0.3556</v>
       </c>
       <c r="V23" t="n">
         <v>8.325099999999999</v>
